--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.56847245591195</v>
+        <v>8.217376774085693</v>
       </c>
       <c r="D2" t="n">
-        <v>49.37267673479502</v>
+        <v>8.023059969404191</v>
       </c>
       <c r="E2" t="n">
-        <v>13.74549889163187</v>
+        <v>2.233643569890178</v>
       </c>
       <c r="F2" t="n">
-        <v>12.85783756902327</v>
+        <v>2.089398604966281</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.62146457635072</v>
+        <v>5.463487993656992</v>
       </c>
       <c r="D3" t="n">
-        <v>34.35019449122962</v>
+        <v>5.581906604824814</v>
       </c>
       <c r="E3" t="n">
-        <v>13.74549889163187</v>
+        <v>2.233643569890178</v>
       </c>
       <c r="F3" t="n">
-        <v>12.85783756902327</v>
+        <v>2.089398604966281</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>72.58042688870698</v>
+        <v>11.79431936941488</v>
       </c>
       <c r="D4" t="n">
-        <v>71.28104197081048</v>
+        <v>11.5831693202567</v>
       </c>
       <c r="E4" t="n">
-        <v>13.74549889163187</v>
+        <v>2.233643569890178</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85783756902327</v>
+        <v>2.089398604966281</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.04472928098614</v>
+        <v>5.532268508160248</v>
       </c>
       <c r="D5" t="n">
-        <v>35.30722799591168</v>
+        <v>5.737424549335649</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74549889163187</v>
+        <v>2.233643569890178</v>
       </c>
       <c r="F5" t="n">
-        <v>12.85783756902327</v>
+        <v>2.089398604966281</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.67801121845962</v>
+        <v>8.560176822999688</v>
       </c>
       <c r="D6" t="n">
-        <v>52.37738320312682</v>
+        <v>8.511324770508109</v>
       </c>
       <c r="E6" t="n">
-        <v>13.74549889163187</v>
+        <v>2.233643569890178</v>
       </c>
       <c r="F6" t="n">
-        <v>12.85783756902327</v>
+        <v>2.089398604966281</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.64044525555276</v>
+        <v>6.116572354027324</v>
       </c>
       <c r="D7" t="n">
-        <v>38.56294097539263</v>
+        <v>6.266477908501303</v>
       </c>
       <c r="E7" t="n">
-        <v>13.74549889163187</v>
+        <v>2.233643569890178</v>
       </c>
       <c r="F7" t="n">
-        <v>12.85783756902327</v>
+        <v>2.089398604966281</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
